--- a/data/trans_orig/P2A_senso_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_senso_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2007</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24181</t>
+          <t>24834</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15404</t>
+          <t>15474</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>15749</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35162</t>
+          <t>34854</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>669831</t>
+          <t>669178</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>684976</t>
+          <t>684598</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>672947</t>
+          <t>672877</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>684266</t>
+          <t>684503</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1347201</t>
+          <t>1347509</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1366742</t>
+          <t>1366614</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24196</t>
+          <t>24967</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25295</t>
+          <t>25515</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21506</t>
+          <t>21111</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44105</t>
+          <t>45086</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>937604</t>
+          <t>936833</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>953802</t>
+          <t>953660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>943098</t>
+          <t>942878</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>959305</t>
+          <t>959159</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1886088</t>
+          <t>1885107</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1908687</t>
+          <t>1909082</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17420</t>
+          <t>16178</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19231</t>
+          <t>18600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>11670</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29643</t>
+          <t>29887</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661089</t>
+          <t>662331</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>674787</t>
+          <t>674757</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>664610</t>
+          <t>665241</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>678405</t>
+          <t>678506</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1332707</t>
+          <t>1332463</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1351092</t>
+          <t>1350680</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7670</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22105</t>
+          <t>22344</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12514</t>
+          <t>12619</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30420</t>
+          <t>30937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23090</t>
+          <t>23117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45326</t>
+          <t>47487</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>920117</t>
+          <t>919878</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>934771</t>
+          <t>934552</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1008192</t>
+          <t>1007675</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1026098</t>
+          <t>1025993</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1935508</t>
+          <t>1933347</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1957744</t>
+          <t>1957717</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38003</t>
+          <t>37661</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>66661</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42733</t>
+          <t>43136</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73473</t>
+          <t>72447</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86200</t>
+          <t>87814</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127504</t>
+          <t>127417</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3210284</t>
+          <t>3209882</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3238540</t>
+          <t>3238882</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3305724</t>
+          <t>3306750</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3336464</t>
+          <t>3336061</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6528237</t>
+          <t>6528324</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6569541</t>
+          <t>6567927</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2012</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29249</t>
+          <t>29293</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,47 +2695,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>17801</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10416</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>29213</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17801</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10640</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>29136</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24569</t>
+          <t>24867</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50199</t>
+          <t>49286</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>674220</t>
+          <t>674176</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>692988</t>
+          <t>692847</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2813,44 +2813,44 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>98,49%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>679249</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>667837</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>686634</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>97,45%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,81%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>98,51%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>679249</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>667914</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>686410</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,82%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1291</t>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1350320</t>
+          <t>1351233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1375950</t>
+          <t>1375652</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9351</t>
+          <t>8916</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27682</t>
+          <t>26313</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32280</t>
+          <t>31883</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25873</t>
+          <t>26487</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53954</t>
+          <t>52370</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>990265</t>
+          <t>991634</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1008596</t>
+          <t>1009031</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>999904</t>
+          <t>1000301</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1019317</t>
+          <t>1019462</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1996177</t>
+          <t>1997761</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2024258</t>
+          <t>2023644</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18171</t>
+          <t>17089</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20674</t>
+          <t>20059</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>10971</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31065</t>
+          <t>30501</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>739452</t>
+          <t>740534</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754608</t>
+          <t>754664</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>756500</t>
+          <t>757115</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>771850</t>
+          <t>771777</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1503732</t>
+          <t>1504296</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523282</t>
+          <t>1523826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8958</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26585</t>
+          <t>25113</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17943</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40196</t>
+          <t>39380</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31628</t>
+          <t>31303</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58131</t>
+          <t>57090</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>921154</t>
+          <t>922626</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>938781</t>
+          <t>939346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1011705</t>
+          <t>1012521</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1033958</t>
+          <t>1033721</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1941509</t>
+          <t>1942550</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1968012</t>
+          <t>1968337</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43387</t>
+          <t>43454</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75044</t>
+          <t>76525</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,34 +4072,34 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>77898</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>62695</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>97628</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>2,19%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>77898</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>62677</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>98308</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112471</t>
+          <t>113441</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>161895</t>
+          <t>160581</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3351735</t>
+          <t>3350254</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3383392</t>
+          <t>3383325</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,42 +4180,42 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3480411</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3460681</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3495614</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>97,81%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3227</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3480411</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3460001</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3495632</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6823193</t>
+          <t>6824507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6872617</t>
+          <t>6871647</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2016</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12936</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20068</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>661864</t>
+          <t>662743</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>672739</t>
+          <t>672585</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>659129</t>
+          <t>658889</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>670031</t>
+          <t>669788</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1327571</t>
+          <t>1327345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1340700</t>
+          <t>1340850</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18417</t>
+          <t>19060</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22608</t>
+          <t>23691</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13224</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34436</t>
+          <t>34492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1004014</t>
+          <t>1003371</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1017994</t>
+          <t>1018312</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1020305</t>
+          <t>1019222</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1036148</t>
+          <t>1036382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2030908</t>
+          <t>2030852</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2052120</t>
+          <t>2052184</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>15415</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13782</t>
+          <t>13774</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7248</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>24936</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>743780</t>
+          <t>744137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>771229</t>
+          <t>771237</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>782713</t>
+          <t>782455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1520177</t>
+          <t>1519627</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1537315</t>
+          <t>1537372</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20453</t>
+          <t>22570</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19445</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>15082</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34517</t>
+          <t>35346</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>917114</t>
+          <t>914997</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931772</t>
+          <t>931266</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1024334</t>
+          <t>1023848</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1037825</t>
+          <t>1037904</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1946829</t>
+          <t>1946000</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1966472</t>
+          <t>1966264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23416</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50009</t>
+          <t>48808</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27272</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52016</t>
+          <t>51329</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54633</t>
+          <t>56035</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90956</t>
+          <t>93225</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3344341</t>
+          <t>3345542</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3370934</t>
+          <t>3371354</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3492526</t>
+          <t>3493213</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3517270</t>
+          <t>3517996</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6847936</t>
+          <t>6845667</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6884259</t>
+          <t>6882857</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2023</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>8055</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23338</t>
+          <t>23196</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26148</t>
+          <t>26973</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20224</t>
+          <t>21288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41996</t>
+          <t>42867</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>612103</t>
+          <t>612245</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>627498</t>
+          <t>627386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>699182</t>
+          <t>698357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>715501</t>
+          <t>715050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1318776</t>
+          <t>1317905</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1340548</t>
+          <t>1339484</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11032</t>
+          <t>10781</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37038</t>
+          <t>36890</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22227</t>
+          <t>21578</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38923</t>
+          <t>38075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34554</t>
+          <t>34299</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67858</t>
+          <t>68665</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1155826</t>
+          <t>1155974</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1181832</t>
+          <t>1182083</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>919728</t>
+          <t>920576</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>936424</t>
+          <t>937073</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2083658</t>
+          <t>2082851</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2116962</t>
+          <t>2117217</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16190</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35982</t>
+          <t>34954</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35653</t>
+          <t>36038</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>532194</t>
+          <t>574782</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59135</t>
+          <t>57711</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>704362</t>
+          <t>684684</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>41,8%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668698</t>
+          <t>669726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>688490</t>
+          <t>688227</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>401172</t>
+          <t>358584</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>897713</t>
+          <t>897328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>933684</t>
+          <t>953362</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1578911</t>
+          <t>1580335</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24818</t>
+          <t>25636</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18291</t>
+          <t>18141</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37146</t>
+          <t>35805</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31410</t>
+          <t>31714</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56037</t>
+          <t>55164</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>902013</t>
+          <t>901195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>917738</t>
+          <t>917312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1057786</t>
+          <t>1059127</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1076641</t>
+          <t>1076791</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1965726</t>
+          <t>1966599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1990353</t>
+          <t>1990049</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56418</t>
+          <t>58510</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>95588</t>
+          <t>99242</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>103513</t>
+          <t>103528</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>941132</t>
+          <t>935404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>176341</t>
+          <t>177115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1103892</t>
+          <t>1053611</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3364229</t>
+          <t>3360575</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3403399</t>
+          <t>3401307</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2771148</t>
+          <t>2776876</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3608767</t>
+          <t>3608752</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6068205</t>
+          <t>6118486</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6995756</t>
+          <t>6994982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_senso_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_senso_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24834</t>
+          <t>24048</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15474</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15749</t>
+          <t>15642</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34854</t>
+          <t>33689</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>669178</t>
+          <t>669964</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>684598</t>
+          <t>685193</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>672877</t>
+          <t>672864</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>684503</t>
+          <t>684477</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1347509</t>
+          <t>1348674</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1366614</t>
+          <t>1366721</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24967</t>
+          <t>24528</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>10189</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25515</t>
+          <t>26268</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21111</t>
+          <t>21304</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45086</t>
+          <t>42892</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>936833</t>
+          <t>937272</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>953660</t>
+          <t>953687</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>942878</t>
+          <t>942125</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>959159</t>
+          <t>958204</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1885107</t>
+          <t>1887301</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1909082</t>
+          <t>1908889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3766</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16178</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18600</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>11821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>30198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>662331</t>
+          <t>662211</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>674757</t>
+          <t>674743</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>665241</t>
+          <t>663808</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>678506</t>
+          <t>677808</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1332463</t>
+          <t>1332152</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1350680</t>
+          <t>1350529</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7670</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22344</t>
+          <t>21137</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12619</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30937</t>
+          <t>31653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23117</t>
+          <t>23598</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47487</t>
+          <t>46465</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>919878</t>
+          <t>921085</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>934552</t>
+          <t>934928</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1007675</t>
+          <t>1006959</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1025993</t>
+          <t>1026277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1933347</t>
+          <t>1934369</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1957717</t>
+          <t>1957236</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37661</t>
+          <t>37702</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66661</t>
+          <t>65606</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43136</t>
+          <t>43055</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72447</t>
+          <t>73542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87814</t>
+          <t>87785</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127417</t>
+          <t>127834</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3209882</t>
+          <t>3210937</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3238882</t>
+          <t>3238841</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3306750</t>
+          <t>3305655</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3336061</t>
+          <t>3336142</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6528324</t>
+          <t>6527907</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6567927</t>
+          <t>6567956</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29293</t>
+          <t>27732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29213</t>
+          <t>28729</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24867</t>
+          <t>26079</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49286</t>
+          <t>50895</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>674176</t>
+          <t>675737</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>692847</t>
+          <t>692860</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>667837</t>
+          <t>668321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>686634</t>
+          <t>686054</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1351233</t>
+          <t>1349624</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1375652</t>
+          <t>1374440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>8978</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26313</t>
+          <t>26807</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>12507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31883</t>
+          <t>32240</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26487</t>
+          <t>25618</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52370</t>
+          <t>50682</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>991634</t>
+          <t>991140</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1009031</t>
+          <t>1008969</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1000301</t>
+          <t>999944</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1019462</t>
+          <t>1019677</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1997761</t>
+          <t>1999449</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2023644</t>
+          <t>2024513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17089</t>
+          <t>16268</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20059</t>
+          <t>20516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10971</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30501</t>
+          <t>32784</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>740534</t>
+          <t>741355</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754664</t>
+          <t>754571</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>757115</t>
+          <t>756658</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>771777</t>
+          <t>771617</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1504296</t>
+          <t>1502013</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523826</t>
+          <t>1522476</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25113</t>
+          <t>26266</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18180</t>
+          <t>19179</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39380</t>
+          <t>40920</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31303</t>
+          <t>31449</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57090</t>
+          <t>58961</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>922626</t>
+          <t>921473</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>939346</t>
+          <t>939306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1012521</t>
+          <t>1010981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1033721</t>
+          <t>1032722</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1942550</t>
+          <t>1940679</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1968337</t>
+          <t>1968191</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43454</t>
+          <t>42672</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76525</t>
+          <t>75290</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62695</t>
+          <t>61273</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97628</t>
+          <t>96951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113441</t>
+          <t>112025</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160581</t>
+          <t>162776</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3350254</t>
+          <t>3351489</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3383325</t>
+          <t>3384107</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3460681</t>
+          <t>3461358</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3495614</t>
+          <t>3497036</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6824507</t>
+          <t>6822312</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6871647</t>
+          <t>6873063</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13950</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20294</t>
+          <t>21280</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>662743</t>
+          <t>661695</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>672585</t>
+          <t>672118</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>658889</t>
+          <t>659151</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>669788</t>
+          <t>669995</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1327345</t>
+          <t>1326359</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1340850</t>
+          <t>1340306</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19060</t>
+          <t>19838</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23691</t>
+          <t>22258</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>13786</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34492</t>
+          <t>35821</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1003371</t>
+          <t>1002593</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1018312</t>
+          <t>1017739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1019222</t>
+          <t>1020655</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1036382</t>
+          <t>1036491</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2030852</t>
+          <t>2029523</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2052184</t>
+          <t>2051558</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2457</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15415</t>
+          <t>17972</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13774</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,47 +5363,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>13708</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>7228</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>27053</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>1,75%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>13708</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>7191</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>24936</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>744137</t>
+          <t>741580</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>757144</t>
+          <t>757095</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>771237</t>
+          <t>770963</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>782455</t>
+          <t>781974</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,42 +5476,42 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>98,21%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1421</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1530855</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1517510</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1537335</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>98,25%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1421</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1530855</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1519627</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1537372</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22570</t>
+          <t>20370</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>19660</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15082</t>
+          <t>14936</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35346</t>
+          <t>35122</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>914997</t>
+          <t>917197</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931266</t>
+          <t>931252</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1023848</t>
+          <t>1024119</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1037904</t>
+          <t>1037632</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1946000</t>
+          <t>1946224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1966264</t>
+          <t>1966410</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>22904</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>50111</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,49 +6014,49 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>37722</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>26305</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>51035</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>37722</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>26546</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>51329</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>65</t>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56035</t>
+          <t>54381</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93225</t>
+          <t>90609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3345542</t>
+          <t>3344239</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3371354</t>
+          <t>3371446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,47 +6127,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3506820</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3493507</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3518237</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>98,94%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>98,56%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3303</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3506820</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3493213</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3517996</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,94%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,55%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6845667</t>
+          <t>6848283</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6882857</t>
+          <t>6884511</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14004</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23196</t>
+          <t>22793</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>18939</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10280</t>
+          <t>12733</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26973</t>
+          <t>30471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>29731</t>
+          <t>33089</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21288</t>
+          <t>23488</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42867</t>
+          <t>45893</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>621437</t>
+          <t>676560</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>612245</t>
+          <t>667917</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>627386</t>
+          <t>682488</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>709603</t>
+          <t>715241</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>698357</t>
+          <t>703709</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>715050</t>
+          <t>721447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1331041</t>
+          <t>1391800</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1317905</t>
+          <t>1378996</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1339484</t>
+          <t>1401401</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,67 +6912,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22618</t>
+          <t>24830</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10781</t>
+          <t>15600</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36890</t>
+          <t>39372</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>33112</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>25476</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>44274</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>3,09%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>29631</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>21578</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>38075</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>52250</t>
+          <t>57942</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34299</t>
+          <t>44954</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68665</t>
+          <t>74852</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -7025,67 +7025,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1170246</t>
+          <t>1024087</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1155974</t>
+          <t>1009545</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1182083</t>
+          <t>1033317</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>96,25%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1038362</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1027200</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1045998</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>96,91%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1464</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>929020</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>920576</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>937073</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,91%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2099266</t>
+          <t>2062449</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2082851</t>
+          <t>2045539</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2117217</t>
+          <t>2075437</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24367</t>
+          <t>32206</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16453</t>
+          <t>22125</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34954</t>
+          <t>47648</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>235946</t>
+          <t>38711</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36038</t>
+          <t>29020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>574782</t>
+          <t>50982</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>260312</t>
+          <t>70917</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57711</t>
+          <t>56004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>684684</t>
+          <t>89290</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>680313</t>
+          <t>770867</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>669726</t>
+          <t>755425</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>688227</t>
+          <t>780948</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>697420</t>
+          <t>773548</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>358584</t>
+          <t>761277</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>897328</t>
+          <t>783239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1377734</t>
+          <t>1544415</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>953362</t>
+          <t>1526042</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1580335</t>
+          <t>1559328</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,17 +7598,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>10579</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25636</t>
+          <t>26689</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26150</t>
+          <t>29923</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>22188</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35805</t>
+          <t>40357</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41916</t>
+          <t>46743</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31714</t>
+          <t>36834</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55164</t>
+          <t>59380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -7711,17 +7711,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>911066</t>
+          <t>973243</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>901195</t>
+          <t>963373</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>917312</t>
+          <t>979483</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1068782</t>
+          <t>1089118</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1059127</t>
+          <t>1078684</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1076791</t>
+          <t>1096853</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1979847</t>
+          <t>2062361</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1966599</t>
+          <t>2049724</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1990049</t>
+          <t>2072270</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,102 +7941,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>76755</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58510</t>
+          <t>69106</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99242</t>
+          <t>110224</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>120685</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>102653</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>141561</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>208690</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>185026</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>238607</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>2,87%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>307454</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>103528</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>935404</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>25,2%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>384209</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>177115</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1053611</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -8054,102 +8054,102 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3383062</t>
+          <t>3444757</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3360575</t>
+          <t>3422538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3401307</t>
+          <t>3463656</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5185</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3616269</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3595393</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3634301</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>96,77%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>96,21%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>97,25%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>8475</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>7061026</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>7031109</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>7084690</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>97,13%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,31%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5185</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3404826</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2776876</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3608752</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>91,72%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>74,8%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>8475</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6787888</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6118486</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6994982</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>94,64%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_senso_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_senso_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
